--- a/scrapers/ubereats_mcdonalds.xlsx
+++ b/scrapers/ubereats_mcdonalds.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -583,24 +583,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paquete Botanero</t>
+          <t>McTrío mediano Cuarto de Libra con Queso</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$125.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>$200.00</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>- 38%</t>
-        </is>
-      </c>
+          <t>$169.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,12 +607,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -630,7 +622,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -645,16 +637,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cajita Feliz McNuggets de pollo 4 pzas</t>
+          <t>Exclusivo Uber</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$149.00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>$159.00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>$228.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>- 30%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,17 +694,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>McTrío mediano Cuarto de Libra con Queso</t>
+          <t>Paquete Botanero</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$169.00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>$119.00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>$200.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>- 41%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,12 +727,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -734,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -744,13 +752,18 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>McTrío mediano BBQ Crispy Onion Doble</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>McTrío mediano Cuarto de Libra Doble con Queso</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>McTrío mediano Cuarto de Libra Doble con Queso
+$199.00</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$229.00</t>
+          <t>$199.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -769,12 +782,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -784,7 +797,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -794,18 +807,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>McTrío mediano Cuarto de Libra Doble con Queso</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>McTrío mediano Cuarto de Libra Doble con Queso
-$199.00</t>
-        </is>
-      </c>
+          <t>McTrío mediano 2 Hamburguesas con Queso</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$199.00</t>
+          <t>$149.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -824,12 +832,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -839,7 +847,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -849,13 +857,13 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>McTrío mediano 2 Hamburguesas con Queso</t>
+          <t>McTrío mediano BBQ Crispy Onion Doble</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$149.00</t>
+          <t>$229.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -874,12 +882,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -889,7 +897,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -899,7 +907,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Exclusivo Uber</t>
+          <t>McTrío Big Mac mediano+McFlurry Oreo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -910,12 +918,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$228.00</t>
+          <t>$218.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>- 26%</t>
+          <t>- 22%</t>
         </is>
       </c>
     </row>
@@ -932,12 +940,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -947,7 +955,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -957,13 +965,13 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>McTrío mediano Big Mac</t>
+          <t>Cajita Feliz McNuggets de pollo 4 pzas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$159.00</t>
+          <t>$149.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -982,12 +990,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -997,7 +1005,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1007,13 +1015,13 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Papas grandes</t>
+          <t>McTrío mediano McNifica</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>$169.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1032,12 +1040,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1047,7 +1055,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1057,23 +1065,23 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>McTrío Big Mac mediano+McFlurry Oreo</t>
+          <t>Paquete Consentidos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>$269.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>$218.00</t>
+          <t>$525.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>- 18%</t>
+          <t>- 49%</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1098,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1105,7 +1113,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1115,13 +1123,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>McTrio mediano McMéxico Pollo</t>
+          <t>McTrío BBQ Crispy Onion mediano 1 carne</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>$199.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1140,12 +1148,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1155,7 +1163,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1165,13 +1173,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Cajita Feliz Hamburguesa Lechuga Tomate</t>
+          <t>McTrio mediano McNuggets 10 pzas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$149.00</t>
+          <t>$169.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1190,12 +1198,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1205,7 +1213,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1215,17 +1223,29 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 6 pzas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>McTrío mediano McPollo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Hamburguesa con pechuga de pollo empanizada, lechuga y mayonesa. Incluye papas y refresco de 21oz.</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>$99.00</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>$115.00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>- 14%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1240,12 +1260,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1255,7 +1275,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1265,23 +1285,23 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Medio Tiempo Familiar</t>
+          <t>Pay de Piña</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>$419.00</t>
+          <t>$29.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>$487.00</t>
+          <t>$40.00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>- 14%</t>
+          <t>- 28%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1318,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1313,7 +1333,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1323,27 +1343,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tripleta Dorada</t>
+          <t>McNuggets y Papas para Todos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3 McTríos Cuartos de Libra + 10 McNuggets</t>
+          <t>30 McNuggets + 2 papas medianas</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>$575.00</t>
+          <t>$289.00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>$652.00</t>
+          <t>$494.00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>- 12%</t>
+          <t>- 41%</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1380,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1375,7 +1395,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1385,27 +1405,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>McPollo o Doble con Queso</t>
+          <t>Paquete Pits</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Elige entre McPollo o Hamburguesa Doble con Queso</t>
+          <t>McFlurry Oreo + Papas Grandes</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>$129.00</t>
+          <t>$89.00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>$158.00</t>
+          <t>$134.00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>- 18%</t>
+          <t>- 34%</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1442,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1437,7 +1457,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1447,27 +1467,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paquete para 4</t>
+          <t>Cajita Feliz  McNuggets Plus</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4 Hamburguesas a elegir + 4 Papas Medianas + 4 Refrescos Medianos</t>
+          <t>Cajita Feliz 4 McNuggets + Hamburguesa con Queso + Papas grandes</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>$529.00</t>
+          <t>$229.00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>$620.00</t>
+          <t>$273.00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>- 15%</t>
+          <t>- 16%</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1504,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1499,7 +1519,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1509,27 +1529,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Para los Penales</t>
+          <t>Exclusivo Uber</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2 Hamburguesas con Queso + 20 McNuggets + 2 Papas grandes + 2 Refrescos medianos</t>
+          <t>McTrío Mediano 10 McNuggets + Hamburguesa con Queso</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>$505.00</t>
+          <t>$159.00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>$585.00</t>
+          <t>$228.00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>- 14%</t>
+          <t>- 30%</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1566,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1561,7 +1581,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1571,27 +1591,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Uber Snack</t>
+          <t>Medio Tiempo Familiar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hamburguesa con Queso + 4 McNuggets + Refresco Chico</t>
+          <t>2 McTríos Cuarto de Libra + 1 Cajita Feliz Nuggets 4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>$103.00</t>
+          <t>$399.00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>$167.00</t>
+          <t>$487.00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>- 38%</t>
+          <t>- 18%</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1628,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1623,7 +1643,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1633,27 +1653,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cajita Feliz  McNuggets Plus</t>
+          <t>Paquete para 4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cajita Feliz 4 McNuggets + Hamburguesa con Queso + Papas grandes</t>
+          <t>4 Hamburguesas a elegir + 4 Papas Medianas + 4 Refrescos Medianos</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>$235.00</t>
+          <t>$489.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>$273.00</t>
+          <t>$620.00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>- 14%</t>
+          <t>- 21%</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1690,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1685,7 +1705,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1695,27 +1715,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paquete Me encanta</t>
+          <t>McTrío Big Mac mediano+McFlurry Oreo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2 Hamburguesas con Queso + 4 Mcnuggets + Refresco Mediano</t>
+          <t>McTrío Mediano Big Mac + McFlurry Oreo</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>$143.00</t>
+          <t>$169.00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>$236.00</t>
+          <t>$218.00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>- 39%</t>
+          <t>- 22%</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1752,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1747,7 +1767,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1767,7 +1787,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>$389.00</t>
+          <t>$359.00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1777,7 +1797,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>- 40%</t>
+          <t>- 45%</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1814,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1809,7 +1829,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1819,27 +1839,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No fue Penal</t>
+          <t>McPollo o Doble con Queso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20 McNuggets + 2 Papas grandes</t>
+          <t>Elige entre McPollo o Hamburguesa Doble con Queso</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>$311.00</t>
+          <t>$129.00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>$349.00</t>
+          <t>$158.00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>- 11%</t>
+          <t>- 18%</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1876,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1871,7 +1891,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1881,27 +1901,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paquete Pits</t>
+          <t>Paquete Consentidos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>McFlurry Oreo + Papas Grandes</t>
+          <t>2 Hamburguesas con Queso + 2 McPollo + 2 Papas Medianas + 6 McNuggets</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>$89.00</t>
+          <t>$269.00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>$128.00</t>
+          <t>$525.00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>- 30%</t>
+          <t>- 49%</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1938,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1933,7 +1953,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1943,27 +1963,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Home Office con Big Mac</t>
+          <t>3x2 McFlurry Oreo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Big Mac + Papas Medianas</t>
+          <t>3X2 McFlurry Oreo</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>$118.00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>$200.00</t>
+          <t>$177.00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>- 51%</t>
+          <t>- 33%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +2000,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1995,7 +2015,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2005,27 +2025,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Exclusivo Uber</t>
+          <t>Tu selección favorita</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>McTrío Mediano 10 McNuggets + Hamburguesa con Queso</t>
+          <t>6 Hamburguesas con Queso + 10 McNuggets + 3 Papas grandes</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>$489.00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>$228.00</t>
+          <t>$724.00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>- 26%</t>
+          <t>- 32%</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2062,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2057,7 +2077,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2067,27 +2087,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paquete Consentidos</t>
+          <t>Home Office con Big Mac</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2 Hamburguesas con Queso + 2 McPollo + 2 Papas Medianas + 6 McNuggets</t>
+          <t>Big Mac + Papas Medianas</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>$291.00</t>
+          <t>$99.00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>$525.00</t>
+          <t>$200.00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>- 45%</t>
+          <t>- 51%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2124,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2119,7 +2139,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2129,29 +2149,21 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>McNuggets y Papas para Todos</t>
+          <t>McTrío Copa Mundial de la FIFA™ BigMac</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30 McNuggets + 2 papas medianas</t>
+          <t>Big Mac + Papas medianas + Blister Salsa Big Mac + Refresco mediano + 1 Vaso coleccionable.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>$311.00</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>$494.00</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>- 37%</t>
-        </is>
-      </c>
+          <t>$229.00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2166,12 +2178,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2181,7 +2193,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2191,29 +2203,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paquete Botanero</t>
+          <t>McTrío Copa Mundial de la FIFA™  10 McNuggets</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Disfruta tus partidos favoritos con 10 McNuggets + Papas grandes</t>
+          <t>10 McNuggets+ Papas medianas + Blister Salsa Big Mac + Refresco mediano + 1 Vaso coleccionable.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>$125.00</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>$200.00</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>- 38%</t>
-        </is>
-      </c>
+          <t>$239.00</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2228,12 +2232,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2253,21 +2257,29 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>McTrío Copa Mundial de la FIFA™ BigMac</t>
+          <t>Tu selección favorita</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Big Mac + Papas medianas + Blister Salsa Big Mac + Refresco mediano + 1 Vaso coleccionable.</t>
+          <t>6 Hamburguesas con Queso + 10 McNuggets + 3 Papas grandes</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>$229.00</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>$489.00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>$724.00</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>- 32%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2282,12 +2294,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2297,7 +2309,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2307,21 +2319,29 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>McTrío Copa Mundial de la FIFA™  10 McNuggets</t>
+          <t>Para los Penales</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10 McNuggets+ Papas medianas + Blister Salsa Big Mac + Refresco mediano + 1 Vaso coleccionable.</t>
+          <t>2 Hamburguesas con Queso + 20 McNuggets + 2 Papas grandes + 2 Refrescos medianos</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>$239.00</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>$485.00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>$585.00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>- 17%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2336,12 +2356,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2351,7 +2371,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2361,27 +2381,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tu selección favorita</t>
+          <t>No fue Penal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6 Hamburguesas con Queso + 10 McNuggets + 3 Papas grandes</t>
+          <t>20 McNuggets + 2 Papas grandes</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>$517.00</t>
+          <t>$299.00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>$724.00</t>
+          <t>$349.00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>- 29%</t>
+          <t>- 14%</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2418,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2413,7 +2433,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2423,27 +2443,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Para los Penales</t>
+          <t>Tripleta Dorada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2 Hamburguesas con Queso + 20 McNuggets + 2 Papas grandes + 2 Refrescos medianos</t>
+          <t>3 McTríos Cuartos de Libra + 10 McNuggets</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>$505.00</t>
+          <t>$535.00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>$585.00</t>
+          <t>$652.00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>- 14%</t>
+          <t>- 18%</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2480,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2475,7 +2495,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2485,27 +2505,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No fue Penal</t>
+          <t>Medio Tiempo Familiar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20 McNuggets + 2 Papas grandes</t>
+          <t>2 McTríos Cuarto de Libra + 1 Cajita Feliz Nuggets 4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>$311.00</t>
+          <t>$399.00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>$349.00</t>
+          <t>$487.00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>- 11%</t>
+          <t>- 18%</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2542,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2537,7 +2557,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2547,29 +2567,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tripleta Dorada</t>
+          <t>Cajita Feliz Hamburguesa con Queso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3 McTríos Cuartos de Libra + 10 McNuggets</t>
+          <t>Pide tu Cajita Feliz de Hamburguesa con Queso; Incluye papas kids y Yoplait</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>$575.00</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>$652.00</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>- 12%</t>
-        </is>
-      </c>
+          <t>$149.00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2584,12 +2596,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2599,7 +2611,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2609,29 +2621,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Medio Tiempo Familiar</t>
+          <t>Cajita Feliz McNuggets de pollo 4 pzas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2 McTríos Cuarto de Libra + 1 Cajita Feliz Nuggets 4</t>
+          <t>Pide tu Cajita Feliz de McNuggets 4 piezas; Incluye papas kids y Yoplait.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>$419.00</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>$487.00</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>- 14%</t>
-        </is>
-      </c>
+          <t>$149.00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2646,12 +2650,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2661,7 +2665,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2671,12 +2675,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Cajita Feliz Hamburguesa con Queso</t>
+          <t>Cajita Feliz Hamburguesa Lechuga Tomate</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Pide tu Cajita Feliz de Hamburguesa con Queso; Incluye papas kids y Yoplait</t>
+          <t>Pide tu Cajita Feliz de Hamburguesa con Lechuga y Tomate; Incluye papas kids y Yoplait.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2700,12 +2704,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2715,7 +2719,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2725,17 +2729,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cajita Feliz McNuggets de pollo 4 pzas</t>
+          <t>Cajita Feliz Hamburguesa sin Queso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Pide tu Cajita Feliz de McNuggets 4 piezas; Incluye papas kids y Yoplait.</t>
+          <t>Pide tu Cajita Feliz de Hamburguesa; Incluye papas kids y Yoplait.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>$149.00</t>
+          <t>$139.00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2754,12 +2758,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2769,7 +2773,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2779,21 +2783,29 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cajita Feliz Hamburguesa Lechuga Tomate</t>
+          <t>McTrío mediano McPollo</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Pide tu Cajita Feliz de Hamburguesa con Lechuga y Tomate; Incluye papas kids y Yoplait.</t>
+          <t>Hamburguesa con pechuga de pollo empanizada, lechuga y mayonesa. Incluye papas y refresco de 21oz.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>$149.00</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>$99.00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>$115.00</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>- 14%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2808,12 +2820,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2823,7 +2835,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2833,17 +2845,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cajita Feliz Hamburguesa sin Queso</t>
+          <t>McTrío mediano Hamburguesa BBQ Cheddar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Pide tu Cajita Feliz de Hamburguesa; Incluye papas kids y Yoplait.</t>
+          <t>McTrío Mediano BBQ Cheddar</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>$139.00</t>
+          <t>$115.00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -2862,12 +2874,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2877,7 +2889,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2887,27 +2899,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>McTrío mediano McPollo</t>
+          <t>Cajita Feliz  McNuggets Plus</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Hamburguesa con pechuga de pollo empanizada, lechuga y mayonesa. Incluye papas y refresco de 21oz.</t>
+          <t>Cajita Feliz 4 McNuggets + Hamburguesa con Queso + Papas grandes</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>$229.00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>$115.00</t>
+          <t>$273.00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>- 14%</t>
+          <t>- 16%</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2936,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2939,7 +2951,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2949,17 +2961,13 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>McTrío mediano Hamburguesa BBQ Cheddar</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>McTrío Mediano BBQ Cheddar</t>
-        </is>
-      </c>
+          <t>McTrío Hamb con Queso</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>$115.00</t>
+          <t>$95.00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2978,12 +2986,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2993,7 +3001,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3003,29 +3011,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Cajita Feliz  McNuggets Plus</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Cajita Feliz 4 McNuggets + Hamburguesa con Queso + Papas grandes</t>
-        </is>
-      </c>
+          <t>McTrío Hamb Dbl con Queso</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>$235.00</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>$273.00</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>- 14%</t>
-        </is>
-      </c>
+          <t>$105.00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3040,12 +3036,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3055,7 +3051,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3065,13 +3061,13 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>McTrío Hamb con Queso</t>
+          <t>McTrío Hamb Triple con Queso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>$95.00</t>
+          <t>$115.00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3090,12 +3086,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3105,7 +3101,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3115,17 +3111,29 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>McTrío Hamb Dbl con Queso</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Paquete Pits</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>McFlurry Oreo + Papas Grandes</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>$105.00</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+          <t>$89.00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>$134.00</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>- 34%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3140,12 +3148,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3155,7 +3163,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3165,17 +3173,29 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>McTrío Hamb Triple con Queso</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Uber Snack</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Hamburguesa con Queso + 4 McNuggets + Refresco Chico</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>$115.00</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+          <t>$99.00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>$167.00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>- 41%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3190,12 +3210,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3205,7 +3225,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3215,27 +3235,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paquete Pits</t>
+          <t>Home Office con Big Mac</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>McFlurry Oreo + Papas Grandes</t>
+          <t>Big Mac + Papas Medianas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>$89.00</t>
+          <t>$99.00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>$128.00</t>
+          <t>$200.00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>- 30%</t>
+          <t>- 51%</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3272,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3267,7 +3287,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3277,27 +3297,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Uber Snack</t>
+          <t>McPollo o Doble con Queso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Hamburguesa con Queso + 4 McNuggets + Refresco Chico</t>
+          <t>Elige entre McPollo o Hamburguesa Doble con Queso</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>$103.00</t>
+          <t>$129.00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>$167.00</t>
+          <t>$158.00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>- 38%</t>
+          <t>- 18%</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3334,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3329,7 +3349,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3339,27 +3359,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Home Office con Big Mac</t>
+          <t>Paquete Me encanta</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Big Mac + Papas Medianas</t>
+          <t>2 Hamburguesas con Queso + 4 Mcnuggets + Refresco Mediano</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>$139.00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>$200.00</t>
+          <t>$236.00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>- 51%</t>
+          <t>- 41%</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3396,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3391,7 +3411,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3401,27 +3421,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>McPollo o Doble con Queso</t>
+          <t>Paquete Botanero</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Elige entre McPollo o Hamburguesa Doble con Queso</t>
+          <t>Disfruta tus partidos favoritos con 10 McNuggets + Papas grandes</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$129.00</t>
+          <t>$119.00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>$158.00</t>
+          <t>$200.00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>- 18%</t>
+          <t>- 41%</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3458,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3453,7 +3473,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3463,27 +3483,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paquete Me encanta</t>
+          <t>Exclusivo Uber</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2 Hamburguesas con Queso + 4 Mcnuggets + Refresco Mediano</t>
+          <t>McTrío Mediano 10 McNuggets + Hamburguesa con Queso</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$143.00</t>
+          <t>$159.00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>$236.00</t>
+          <t>$228.00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>- 39%</t>
+          <t>- 30%</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3520,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3515,7 +3535,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3525,27 +3545,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paquete Botanero</t>
+          <t>McTrío Big Mac mediano+McFlurry Oreo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Disfruta tus partidos favoritos con 10 McNuggets + Papas grandes</t>
+          <t>McTrío Mediano Big Mac + McFlurry Oreo</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$125.00</t>
+          <t>$169.00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>$200.00</t>
+          <t>$218.00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>- 38%</t>
+          <t>- 22%</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3582,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3577,7 +3597,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3587,27 +3607,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Exclusivo Uber</t>
+          <t>Paquete Consentidos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>McTrío Mediano 10 McNuggets + Hamburguesa con Queso</t>
+          <t>2 Hamburguesas con Queso + 2 McPollo + 2 Papas Medianas + 6 McNuggets</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>$269.00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>$228.00</t>
+          <t>$525.00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>- 26%</t>
+          <t>- 49%</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3644,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3639,7 +3659,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3649,27 +3669,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>McTrío Big Mac mediano+McFlurry Oreo</t>
+          <t>McNuggets y Papas para Todos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>McTrío Mediano Big Mac + McFlurry Oreo</t>
+          <t>30 McNuggets + 2 papas medianas</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>$289.00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>$218.00</t>
+          <t>$494.00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>- 18%</t>
+          <t>- 41%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3706,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3701,7 +3721,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3711,22 +3731,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paquete Consentidos</t>
+          <t>Para compartir con Bebidas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2 Hamburguesas con Queso + 2 McPollo + 2 Papas Medianas + 6 McNuggets</t>
+          <t>4 Hamburguesas con Queso + 10 McNuggets + 2 Papas Grandes + 2 Refrescos Medianos</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$291.00</t>
+          <t>$359.00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>$525.00</t>
+          <t>$649.00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3748,12 +3768,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3763,7 +3783,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3773,27 +3793,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>McNuggets y Papas para Todos</t>
+          <t>Paquete para 4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>30 McNuggets + 2 papas medianas</t>
+          <t>4 Hamburguesas a elegir + 4 Papas Medianas + 4 Refrescos Medianos</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$311.00</t>
+          <t>$489.00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>$494.00</t>
+          <t>$620.00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>- 37%</t>
+          <t>- 21%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3830,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3825,7 +3845,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3835,29 +3855,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Para compartir con Bebidas</t>
+          <t>McTrío mediano Big Mac</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4 Hamburguesas con Queso + 10 McNuggets + 2 Papas Grandes + 2 Refrescos Medianos</t>
+          <t>Hamburguesa con 2 carnes de res, con salsa especial de Big Mac y queso derretido. Incluye papas y refresco de 21oz.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$389.00</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>$649.00</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>- 40%</t>
-        </is>
-      </c>
+          <t>$159.00</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3872,12 +3884,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3887,7 +3899,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3897,29 +3909,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paquete para 4</t>
+          <t>McTrío mediano Cuarto de Libra con Queso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4 Hamburguesas a elegir + 4 Papas Medianas + 4 Refrescos Medianos</t>
+          <t>Hamburguesa con carne de res, sazonada con una pizca de sal y pimienta con queso americano, cebolla, pepinillos, cátsup y mostaza.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$529.00</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>$620.00</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>- 15%</t>
-        </is>
-      </c>
+          <t>$169.00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3934,12 +3938,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3949,7 +3953,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3959,17 +3963,13 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>McTrío mediano Big Mac</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Hamburguesa con 2 carnes de res, con salsa especial de Big Mac y queso derretido. Incluye papas y refresco de 21oz.</t>
-        </is>
-      </c>
+          <t>McTrio mediano McNuggets 10 pzas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$159.00</t>
+          <t>$169.00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4013,17 +4013,13 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>McTrío mediano Cuarto de Libra con Queso</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Hamburguesa con carne de res, sazonada con una pizca de sal y pimienta con queso americano, cebolla, pepinillos, cátsup y mostaza.</t>
-        </is>
-      </c>
+          <t>McTrío mediano 2 Hamburguesas con Queso</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>$149.00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4042,12 +4038,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4057,7 +4053,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4067,13 +4063,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>McTrio mediano McNuggets 10 pzas</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>McTrío mediano McTocino</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Disfruta de una Hamburguesa McTocino, Papas Medianas y Refresco Mediano.</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>$159.00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4092,12 +4092,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4117,13 +4117,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>McTrío mediano 2 Hamburguesas con Queso</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>McTrío mediano McNifica</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Hamburguesa con 1 carne de res, queso tipo americano, lechuga, cebolla, dos rebanadas de jitomate, mayonesa, cátsup, mostaza.</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$149.00</t>
+          <t>$169.00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4142,12 +4146,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4157,7 +4161,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4167,17 +4171,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>McTrío mediano McTocino</t>
+          <t>McTrío mediano McCrispy Cajún</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Disfruta de una Hamburguesa McTocino, Papas Medianas y Refresco Mediano.</t>
+          <t>McTrío Mediano McCrispy Cajún</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$159.00</t>
+          <t>$179.00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4196,12 +4200,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4211,7 +4215,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4221,12 +4225,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>McTrío mediano McNifica</t>
+          <t>McTrío mediano McCrispy Deluxe</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Hamburguesa con 1 carne de res, queso tipo americano, lechuga, cebolla, dos rebanadas de jitomate, mayonesa, cátsup, mostaza.</t>
+          <t>McTrío McCrispy Deluxe</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4250,12 +4254,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4265,7 +4269,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4275,17 +4279,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>McTrío mediano McCrispy Cajún</t>
+          <t>McTrío mediano McCrispy Spicy</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>McTrío Mediano McCrispy Cajún</t>
+          <t>McTrio Mediano McCrispy Spicy</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>$159.00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4304,12 +4308,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4319,7 +4323,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4329,17 +4333,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>McTrío mediano McCrispy Deluxe</t>
+          <t>McTrío mediano McUSA</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>McTrío McCrispy Deluxe</t>
+          <t>McUSA es una deliciosa hamburguesa que resalta los sabores tradicionales de Estados Unidos, con doble carne jugosa, queso cheddar, tocino crujiente, pepinillos, cebolla asada y salsa BBQ, creada especialmente como parte de la campaña Mundialistas para celebrar la pasión por el fútbol.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>$219.00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4358,12 +4362,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4373,7 +4377,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4383,17 +4387,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>McTrío mediano McCrispy Spicy</t>
+          <t>McTrio mediano McMéxico Pollo</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>McTrio Mediano McCrispy Spicy</t>
+          <t>La McMéxico es una deliciosa hamburguesa en colaboración con Tajín®, preparada con doble carne jugosa, tocino crujiente, queso blanco, lechuga fresca, cebolla y una irresistible salsa cremosa Tajín®</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$159.00</t>
+          <t>$179.00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4412,12 +4416,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4427,7 +4431,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4437,17 +4441,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>McTrío mediano McUSA</t>
+          <t>McTrío mediano McFrancia</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>McUSA es una deliciosa hamburguesa que resalta los sabores tradicionales de Estados Unidos, con doble carne jugosa, queso cheddar, tocino crujiente, pepinillos, cebolla asada y salsa BBQ, creada especialmente como parte de la campaña Mundialistas para celebrar la pasión por el fútbol.</t>
+          <t>McFrancia combina sabores clásicos con un toque gourmet, preparada con pollo crujiente de McCrispy, queso cheddar, tocino, lechuga fresca, cebolla caramelizada y el inconfundible aderezo CBO,</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$219.00</t>
+          <t>$179.00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4466,12 +4470,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4481,7 +4485,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4491,7 +4495,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>McTrio mediano McMéxico Pollo</t>
+          <t>McTrio mediano McMéxico Res</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4501,7 +4505,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>$219.00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4520,12 +4524,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4535,7 +4539,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4545,17 +4549,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>McTrío mediano McFrancia</t>
+          <t>McTrío Grands BBQ Triple grande</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>McFrancia combina sabores clásicos con un toque gourmet, preparada con pollo crujiente de McCrispy, queso cheddar, tocino, lechuga fresca, cebolla caramelizada y el inconfundible aderezo CBO,</t>
+          <t>McTrio Mediano Grand Tasty BBQ Doble</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>$269.00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4574,12 +4578,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4589,7 +4593,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4599,17 +4603,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>McTrio mediano McMéxico Res</t>
+          <t>McTrío mediano Grand BBQ Doble</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>La McMéxico es una deliciosa hamburguesa en colaboración con Tajín®, preparada con doble carne jugosa, tocino crujiente, queso blanco, lechuga fresca, cebolla y una irresistible salsa cremosa Tajín®</t>
+          <t>McTrío Mediano Grand BBQ Bacon Doble</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$219.00</t>
+          <t>$239.00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4628,12 +4632,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4643,7 +4647,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4653,17 +4657,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>McTrío Grands BBQ Triple grande</t>
+          <t>McTrío mediano Cuarto de Libra Doble con Queso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>McTrio Mediano Grand Tasty BBQ Doble</t>
+          <t>Hamburguesa con 2 carnes de res, queso americano, cebolla, pepinillos, cátsup y mostaza. Incluye papas y refresco de 21oz.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$269.00</t>
+          <t>$199.00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4682,12 +4686,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4697,7 +4701,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4707,17 +4711,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>McTrío mediano Grand BBQ Doble</t>
+          <t>McTrío Grand Bacon Deluxe Triple mediano</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>McTrío Mediano Grand BBQ Bacon Doble</t>
+          <t>Hamburguesa Grand Bacon Deluxe Triple + Papas Medianas + Refresco Mediano</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$239.00</t>
+          <t>$269.00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -4736,12 +4740,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4751,7 +4755,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4761,17 +4765,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>McTrío mediano Cuarto de Libra Doble con Queso</t>
+          <t>McTrío mediano CBO Doble</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Hamburguesa con 2 carnes de res, queso americano, cebolla, pepinillos, cátsup y mostaza. Incluye papas y refresco de 21oz.</t>
+          <t>Hamburguesa con 2 Carnes Signature, queso cheddar, tocino y cebolla. Incluye papas y refresco de 21oz.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$199.00</t>
+          <t>$229.00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -4790,12 +4794,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4805,7 +4809,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4815,17 +4819,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>McTrío Grand Bacon Deluxe Triple mediano</t>
+          <t>McTrío mediano Club House Doble</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Hamburguesa Grand Bacon Deluxe Triple + Papas Medianas + Refresco Mediano</t>
+          <t>Hamburguesa con 2 Carnes Signature, pan tipo brioche, lechuga, jitomate, queso cheddar, tocino y salsa especial. Incluye papas y refresco de 21oz.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$269.00</t>
+          <t>$229.00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -4844,12 +4848,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4859,7 +4863,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4869,17 +4873,13 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>McTrío mediano CBO Doble</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Hamburguesa con 2 Carnes Signature, queso cheddar, tocino y cebolla. Incluye papas y refresco de 21oz.</t>
-        </is>
-      </c>
+          <t>McTrío mediano McNuggets 20 pzas</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$229.00</t>
+          <t>$219.00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4923,17 +4923,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>McTrío mediano Club House Doble</t>
+          <t>McTrío BBQ Crispy Onion mediano 1 carne</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Hamburguesa con 2 Carnes Signature, pan tipo brioche, lechuga, jitomate, queso cheddar, tocino y salsa especial. Incluye papas y refresco de 21oz.</t>
+          <t>Hamburguesa con 1 Carne Signature, salsa BBQ, cebolla caramelizada, queso cheddar blanco, csrispy onion, tocino y pan brioche. Incluye papas y refresco de 21oz</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$229.00</t>
+          <t>$199.00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4977,13 +4977,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>McTrío mediano McNuggets 20 pzas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>McTrío mediano BBQ Crispy Onion Doble</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Hamburguesa con 2 Carnes Signature, salsa BBQ, cebolla caramelizada, queso cheddar blanco, csrispy onion, tocino y pan brioche.</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$219.00</t>
+          <t>$229.00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5002,12 +5006,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5017,7 +5021,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5027,17 +5031,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>McTrío BBQ Crispy Onion mediano 1 carne</t>
+          <t>Hamburguesa Doble con Queso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Hamburguesa con 1 Carne Signature, salsa BBQ, cebolla caramelizada, queso cheddar blanco, csrispy onion, tocino y pan brioche. Incluye papas y refresco de 21oz</t>
+          <t>Hamburguesa con 2 carnes de res, queso tipo americano, pepinillos, cebolla, cátsup y mostaza</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$199.00</t>
+          <t>$69.00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5056,12 +5060,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5071,7 +5075,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5081,17 +5085,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>McTrío mediano BBQ Crispy Onion Doble</t>
+          <t>McNuggets de Pollo 4 pzas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Hamburguesa con 2 Carnes Signature, salsa BBQ, cebolla caramelizada, queso cheddar blanco, csrispy onion, tocino y pan brioche.</t>
+          <t>4 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$229.00</t>
+          <t>$59.00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5110,12 +5114,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5125,7 +5129,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5135,17 +5139,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Hamburguesa Doble con Queso</t>
+          <t>McNuggets de Pollo 10 pzas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Hamburguesa con 2 carnes de res, queso tipo americano, pepinillos, cebolla, cátsup y mostaza</t>
+          <t>10 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$69.00</t>
+          <t>$145.00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5164,12 +5168,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5179,7 +5183,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5189,12 +5193,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 4 pzas</t>
+          <t>Hamburguesa con Queso</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
+          <t>Hamburguesa con carne de res, queso tipo americano, pepinillos, cebolla, cátsup y mostaza</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5218,12 +5222,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5233,7 +5237,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5243,17 +5247,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 10 pzas</t>
+          <t>Papas grandes</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>10 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
+          <t>Papas a la francesa clasicas doraditas y crujientes por fuera.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>$75.00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5272,12 +5276,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5287,7 +5291,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5297,17 +5301,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Hamburguesa con Queso</t>
+          <t>Big Mac</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Hamburguesa con carne de res, queso tipo americano, pepinillos, cebolla, cátsup y mostaza</t>
+          <t>Hamburguesa con 2 carnes de res, con salsa especial de Big Mac y queso derretido</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$59.00</t>
+          <t>$135.00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5326,12 +5330,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5341,7 +5345,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5351,17 +5355,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Papas grandes</t>
+          <t>Cuarto De Libra Con Queso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Papas a la francesa clasicas doraditas y crujientes por fuera.</t>
+          <t>Hamburguesa con carne de res, queso americano, cebolla, pepinillos, cátsup y mostaza</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>$145.00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5380,12 +5384,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5395,7 +5399,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5405,17 +5409,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Big Mac</t>
+          <t>McNífica</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Hamburguesa con 2 carnes de res, con salsa especial de Big Mac y queso derretido</t>
+          <t>Hamburguesa con carne de res, queso tipo americano, lechuga, cebolla, dos rebanadas de jitomate, mayonesa, cátsup, mostaza</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$135.00</t>
+          <t>$145.00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5434,12 +5438,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5449,7 +5453,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5459,17 +5463,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Cuarto De Libra Con Queso</t>
+          <t>McPollo</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Hamburguesa con carne de res, queso americano, cebolla, pepinillos, cátsup y mostaza</t>
+          <t>Hamburguesa de pechuga de pollo empanizada, lechuga y mayonesa.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>$89.00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5488,12 +5492,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5503,7 +5507,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5513,17 +5517,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>McNífica</t>
+          <t>McNuggets de Pollo 6 pzas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Hamburguesa con carne de res, queso tipo americano, lechuga, cebolla, dos rebanadas de jitomate, mayonesa, cátsup, mostaza</t>
+          <t>6 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>$99.00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5542,12 +5546,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5557,7 +5561,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5567,17 +5571,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>McPollo</t>
+          <t>McNuggets de Pollo 20 pzas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Hamburguesa de pechuga de pollo empanizada, lechuga y mayonesa.</t>
+          <t>20 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$89.00</t>
+          <t>$199.00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5596,12 +5600,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5611,7 +5615,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5621,17 +5625,13 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 6 pzas</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>6 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
-        </is>
-      </c>
+          <t>McFlurry Oreo</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>$59.00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5675,21 +5675,29 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 20 pzas</t>
+          <t>Pay de manzana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>20 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
+          <t>Pay de manzana crujiente y dorado con trozos de manzana y una pizca de canela por dentro.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$199.00</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+          <t>$29.00</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>$40.00</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>- 28%</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5704,12 +5712,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5719,7 +5727,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5729,13 +5737,13 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>McFlurry Oreo</t>
+          <t>McFlurry M&amp;M's</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$59.00</t>
+          <t>$65.00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -5754,12 +5762,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5769,7 +5777,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5779,29 +5787,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Pay de manzana</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Pay de manzana crujiente y dorado con trozos de manzana y una pizca de canela por dentro.</t>
-        </is>
-      </c>
+          <t>Sundae chocolate</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$29.00</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>$40.00</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>- 28%</t>
-        </is>
-      </c>
+          <t>$45.00</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5816,12 +5812,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5831,7 +5827,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5841,10 +5837,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>McFlurry M&amp;M's</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Malteada vainilla</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Malteada con base de helado de leche con sabor vainilla</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>$65.00</t>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Malteada chocolate</t>
+          <t>Malteada fresa</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Malteada con base de helado de leche con jarabe de chocolate.</t>
+          <t>Malteada con base de helado de leche con jarabe de fresa.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sundae chocolate</t>
+          <t>Sundae fresa</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Malteada vainilla</t>
+          <t>Malteada chocolate</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Malteada con base de helado de leche con sabor vainilla</t>
+          <t>Malteada con base de helado de leche con jarabe de chocolate.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6049,14 +6049,10 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Malteada fresa</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Malteada con base de helado de leche con jarabe de fresa.</t>
-        </is>
-      </c>
+          <t>McFlurry Emperador</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>$65.00</t>
@@ -6078,12 +6074,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6093,7 +6089,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6103,17 +6099,29 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sundae fresa</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>3x2 McFlurry Oreo</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3X2 McFlurry Oreo</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$45.00</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+          <t>$118.00</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>$177.00</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>- 33%</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6128,12 +6136,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6143,7 +6151,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6153,17 +6161,25 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>McFlurry Emperador</t>
+          <t>Pay de Piña</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>$65.00</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+          <t>$29.00</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>$40.00</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>- 28%</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6178,12 +6194,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6193,7 +6209,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6203,29 +6219,21 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3x2 McFlurry Oreo</t>
+          <t>Coca-Cola mediana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3X2 McFlurry Oreo</t>
+          <t>Refréscate con Coca Cola de 21 oz</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>$118.00</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>$177.00</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>- 33%</t>
-        </is>
-      </c>
+          <t>$59.00</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6240,12 +6248,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6255,7 +6263,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6265,25 +6273,21 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pay de Piña</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Café Americano grande</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Disfruta de un café recien preparado.</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>$29.00</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>$40.00</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>- 28%</t>
-        </is>
-      </c>
+          <t>$39.00</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6298,12 +6302,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6313,7 +6317,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6323,17 +6327,17 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Coca-Cola mediana</t>
+          <t>Agua Ciel 600 ml</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Refréscate con Coca Cola de 21 oz</t>
+          <t>Refréscate con nuestra presentación de 600ml</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>$59.00</t>
+          <t>$39.00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6352,12 +6356,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6367,7 +6371,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6377,17 +6381,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Café Americano grande</t>
+          <t>Coca-Cola Zero mediana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Disfruta de un café recien preparado.</t>
+          <t>Coca Zero Mediana</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>$39.00</t>
+          <t>$59.00</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6406,12 +6410,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6421,7 +6425,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6431,17 +6435,13 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Coca-Cola Zero mediana</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Coca Zero Mediana</t>
-        </is>
-      </c>
+          <t>Jugo Del Valle Manzana Pet</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>$59.00</t>
+          <t>$39.00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6460,12 +6460,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6485,13 +6485,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Jugo Del Valle Manzana Pet</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Fanta sin azúcar mediana</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Refréscate con Fanta de Naranja de 21 oz</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>$39.00</t>
+          <t>$59.00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -6510,12 +6514,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6525,7 +6529,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6535,17 +6539,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Fanta sin azúcar mediana</t>
+          <t>Café Americano mediano</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Refréscate con Fanta de Naranja de 21 oz</t>
+          <t>Disfruta de un café recien preparado.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>$59.00</t>
+          <t>$35.00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -6564,12 +6568,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>McDonald's Palma</t>
+          <t>McDonald's Taller</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
+          <t>Av. Del Taller 370, Delegación Venustiano Carranza, 15980 Ciudad De México, Cdmx, Mexico, CDMX 15980</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6579,7 +6583,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6589,75 +6593,21 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Café Americano mediano</t>
+          <t>Sprite sin azúcar mediano</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Disfruta de un café recien preparado.</t>
+          <t>Sprite Sin Azúcar Mediano</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>$35.00</t>
+          <t>$59.00</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Uber Eats</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>C. Tlaxcoaque, Centro, Cuauhtémoc, 06080 Ciudad de México, CDMX, México</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>McDonald's Palma</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Calle De Tacuba 80, Centro Histórico, Centro, 06000 Ciudad De México, Cdmx, Mexico, CDMX 06000</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Calle Tlaxcoaque</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>10 min</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Costo de envío: MXN0 (usuarios nuevos)</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sprite sin azúcar mediano</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Sprite Sin Azúcar Mediano</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>$59.00</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
